--- a/UTCUTS/A1_Outputs/reference_works/A-O_Demand_REF.xlsx
+++ b/UTCUTS/A1_Outputs/reference_works/A-O_Demand_REF.xlsx
@@ -6758,7 +6758,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B53FE96F-7C30-4264-8D0D-17E0F671F5E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9062F73-EB9F-4179-A076-E48C3284BFF4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
